--- a/SuRGE_Sharepoint/data/algalIndicators/pigments/surgeFilteredVolumes.xlsx
+++ b/SuRGE_Sharepoint/data/algalIndicators/pigments/surgeFilteredVolumes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/beaulieu_jake_epa_gov/Documents/gitRepository/SuRGE/SuRGE_Sharepoint/data/algalIndicators/pigments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2806" documentId="8_{22E5D3D4-EB3E-4FEE-881A-46F2F5A0A575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67F96F1E-F073-48F6-8F98-0B581BF38F4B}"/>
+  <xr:revisionPtr revIDLastSave="2809" documentId="8_{22E5D3D4-EB3E-4FEE-881A-46F2F5A0A575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D28616E-D864-4450-B5BF-35E18D83E583}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="18696" xr2:uid="{A120EDF9-FC94-4E5E-BD62-FEBBBCE13E35}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$H$461</definedName>
   </definedNames>
-  <calcPr calcId="191028" concurrentManualCount="4"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -633,9 +633,6 @@
     <t>07.31.2021</t>
   </si>
   <si>
-    <t>069-lacustrine</t>
-  </si>
-  <si>
     <t>06.24.2021</t>
   </si>
   <si>
@@ -1114,6 +1111,9 @@
   </si>
   <si>
     <t>08.24.2023</t>
+  </si>
+  <si>
+    <t>069_lacustrine</t>
   </si>
 </sst>
 </file>
@@ -1596,7 +1596,7 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -7778,7 +7778,7 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
-        <v>141</v>
+        <v>301</v>
       </c>
       <c r="B215">
         <v>4</v>
@@ -7790,10 +7790,10 @@
         <v>11</v>
       </c>
       <c r="E215" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F215" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G215">
         <v>935</v>
@@ -7807,7 +7807,7 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>141</v>
+        <v>301</v>
       </c>
       <c r="B216">
         <v>4</v>
@@ -7819,10 +7819,10 @@
         <v>20</v>
       </c>
       <c r="E216" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F216" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G216">
         <v>950</v>
@@ -7836,7 +7836,7 @@
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B217">
         <v>4</v>
@@ -7865,7 +7865,7 @@
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B218">
         <v>4</v>
@@ -7894,7 +7894,7 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B219">
         <v>4</v>
@@ -7923,7 +7923,7 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B220">
         <v>4</v>
@@ -7952,7 +7952,7 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B221">
         <v>4</v>
@@ -7981,7 +7981,7 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B222">
         <v>4</v>
@@ -8010,7 +8010,7 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B223">
         <v>4</v>
@@ -8039,7 +8039,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B224">
         <v>4</v>
@@ -8068,7 +8068,7 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B225">
         <v>4</v>
@@ -8097,7 +8097,7 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B226">
         <v>4</v>
@@ -8126,7 +8126,7 @@
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B227" s="3">
         <v>5</v>
@@ -8138,10 +8138,10 @@
         <v>11</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G227" s="3">
         <v>250</v>
@@ -8155,7 +8155,7 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B228" s="3">
         <v>5</v>
@@ -8167,10 +8167,10 @@
         <v>20</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G228" s="3">
         <v>250</v>
@@ -8184,7 +8184,7 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B229" s="3">
         <v>7</v>
@@ -8213,7 +8213,7 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B230" s="3">
         <v>7</v>
@@ -8242,7 +8242,7 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B231">
         <v>8</v>
@@ -8271,7 +8271,7 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B232">
         <v>8</v>
@@ -8326,7 +8326,7 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B234">
         <v>10</v>
@@ -8355,7 +8355,7 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B235">
         <v>10</v>
@@ -8384,7 +8384,7 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B236">
         <v>10</v>
@@ -8413,7 +8413,7 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B237">
         <v>10</v>
@@ -8442,7 +8442,7 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B238">
         <v>10</v>
@@ -8471,7 +8471,7 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B239">
         <v>10</v>
@@ -8500,7 +8500,7 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B240">
         <v>3</v>
@@ -8529,7 +8529,7 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B241">
         <v>3</v>
@@ -8558,22 +8558,22 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B242">
+        <v>20</v>
+      </c>
+      <c r="C242" t="s">
+        <v>10</v>
+      </c>
+      <c r="D242" t="s">
+        <v>11</v>
+      </c>
+      <c r="E242" t="s">
         <v>151</v>
       </c>
-      <c r="B242">
-        <v>20</v>
-      </c>
-      <c r="C242" t="s">
-        <v>10</v>
-      </c>
-      <c r="D242" t="s">
-        <v>11</v>
-      </c>
-      <c r="E242" t="s">
+      <c r="F242" t="s">
         <v>152</v>
-      </c>
-      <c r="F242" t="s">
-        <v>153</v>
       </c>
       <c r="G242">
         <v>200</v>
@@ -8582,7 +8582,7 @@
         <v>0</v>
       </c>
       <c r="I242" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J242">
         <v>1</v>
@@ -8590,22 +8590,22 @@
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B243">
+        <v>20</v>
+      </c>
+      <c r="C243" t="s">
+        <v>10</v>
+      </c>
+      <c r="D243" t="s">
+        <v>20</v>
+      </c>
+      <c r="E243" t="s">
         <v>151</v>
       </c>
-      <c r="B243">
-        <v>20</v>
-      </c>
-      <c r="C243" t="s">
-        <v>10</v>
-      </c>
-      <c r="D243" t="s">
-        <v>20</v>
-      </c>
-      <c r="E243" t="s">
+      <c r="F243" t="s">
         <v>152</v>
-      </c>
-      <c r="F243" t="s">
-        <v>153</v>
       </c>
       <c r="G243">
         <v>200</v>
@@ -8614,7 +8614,7 @@
         <v>0</v>
       </c>
       <c r="I243" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J243">
         <v>1</v>
@@ -8622,7 +8622,7 @@
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B244">
         <v>3</v>
@@ -8634,10 +8634,10 @@
         <v>11</v>
       </c>
       <c r="E244" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F244" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G244">
         <v>800</v>
@@ -8646,7 +8646,7 @@
         <v>0</v>
       </c>
       <c r="I244" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J244">
         <v>1</v>
@@ -8654,7 +8654,7 @@
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B245">
         <v>3</v>
@@ -8666,10 +8666,10 @@
         <v>20</v>
       </c>
       <c r="E245" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F245" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G245">
         <v>800</v>
@@ -8678,7 +8678,7 @@
         <v>0</v>
       </c>
       <c r="I245" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J245">
         <v>1</v>
@@ -8686,7 +8686,7 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B246">
         <v>3</v>
@@ -8698,10 +8698,10 @@
         <v>11</v>
       </c>
       <c r="E246" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F246" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G246">
         <v>800</v>
@@ -8710,7 +8710,7 @@
         <v>0</v>
       </c>
       <c r="I246" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J246">
         <v>1</v>
@@ -8718,7 +8718,7 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B247">
         <v>3</v>
@@ -8730,10 +8730,10 @@
         <v>20</v>
       </c>
       <c r="E247" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F247" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G247">
         <v>800</v>
@@ -8742,7 +8742,7 @@
         <v>0</v>
       </c>
       <c r="I247" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J247">
         <v>1</v>
@@ -8750,7 +8750,7 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B248">
         <v>3</v>
@@ -8762,10 +8762,10 @@
         <v>11</v>
       </c>
       <c r="E248" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F248" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G248">
         <v>800</v>
@@ -8774,7 +8774,7 @@
         <v>0</v>
       </c>
       <c r="I248" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J248">
         <v>1</v>
@@ -8782,7 +8782,7 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B249">
         <v>3</v>
@@ -8794,10 +8794,10 @@
         <v>20</v>
       </c>
       <c r="E249" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F249" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G249">
         <v>800</v>
@@ -8806,7 +8806,7 @@
         <v>0</v>
       </c>
       <c r="I249" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J249">
         <v>1</v>
@@ -8814,22 +8814,22 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B250">
+        <v>11</v>
+      </c>
+      <c r="C250" t="s">
+        <v>10</v>
+      </c>
+      <c r="D250" t="s">
+        <v>11</v>
+      </c>
+      <c r="E250" t="s">
         <v>157</v>
       </c>
-      <c r="B250">
-        <v>11</v>
-      </c>
-      <c r="C250" t="s">
-        <v>10</v>
-      </c>
-      <c r="D250" t="s">
-        <v>11</v>
-      </c>
-      <c r="E250" t="s">
-        <v>158</v>
-      </c>
       <c r="F250" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G250">
         <v>500</v>
@@ -8838,7 +8838,7 @@
         <v>0</v>
       </c>
       <c r="I250" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J250">
         <v>1</v>
@@ -8846,22 +8846,22 @@
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B251">
+        <v>11</v>
+      </c>
+      <c r="C251" t="s">
+        <v>10</v>
+      </c>
+      <c r="D251" t="s">
+        <v>20</v>
+      </c>
+      <c r="E251" t="s">
         <v>157</v>
       </c>
-      <c r="B251">
-        <v>11</v>
-      </c>
-      <c r="C251" t="s">
-        <v>10</v>
-      </c>
-      <c r="D251" t="s">
-        <v>20</v>
-      </c>
-      <c r="E251" t="s">
-        <v>158</v>
-      </c>
       <c r="F251" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G251">
         <v>600</v>
@@ -8870,7 +8870,7 @@
         <v>0</v>
       </c>
       <c r="I251" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J251">
         <v>1</v>
@@ -8878,7 +8878,7 @@
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B252">
         <v>13</v>
@@ -8890,10 +8890,10 @@
         <v>11</v>
       </c>
       <c r="E252" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F252" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G252">
         <v>800</v>
@@ -8902,7 +8902,7 @@
         <v>0</v>
       </c>
       <c r="I252" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J252">
         <v>1</v>
@@ -8910,7 +8910,7 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B253">
         <v>13</v>
@@ -8922,10 +8922,10 @@
         <v>20</v>
       </c>
       <c r="E253" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F253" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G253">
         <v>800</v>
@@ -8934,7 +8934,7 @@
         <v>0</v>
       </c>
       <c r="I253" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J253">
         <v>1</v>
@@ -8942,7 +8942,7 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B254">
         <v>13</v>
@@ -8954,10 +8954,10 @@
         <v>11</v>
       </c>
       <c r="E254" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F254" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G254">
         <v>400</v>
@@ -8966,7 +8966,7 @@
         <v>0</v>
       </c>
       <c r="I254" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J254">
         <v>1</v>
@@ -8974,7 +8974,7 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B255">
         <v>13</v>
@@ -8986,10 +8986,10 @@
         <v>20</v>
       </c>
       <c r="E255" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F255" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G255">
         <v>400</v>
@@ -8998,7 +8998,7 @@
         <v>0</v>
       </c>
       <c r="I255" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J255">
         <v>1</v>
@@ -9006,7 +9006,7 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B256">
         <v>13</v>
@@ -9018,10 +9018,10 @@
         <v>11</v>
       </c>
       <c r="E256" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F256" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G256">
         <v>400</v>
@@ -9030,7 +9030,7 @@
         <v>0</v>
       </c>
       <c r="I256" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J256">
         <v>1</v>
@@ -9038,7 +9038,7 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B257">
         <v>13</v>
@@ -9050,10 +9050,10 @@
         <v>20</v>
       </c>
       <c r="E257" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F257" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G257">
         <v>400</v>
@@ -9062,7 +9062,7 @@
         <v>0</v>
       </c>
       <c r="I257" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J257">
         <v>1</v>
@@ -9070,7 +9070,7 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B258">
         <v>4</v>
@@ -9082,10 +9082,10 @@
         <v>11</v>
       </c>
       <c r="E258" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F258" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G258">
         <v>800</v>
@@ -9094,7 +9094,7 @@
         <v>0</v>
       </c>
       <c r="I258" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J258">
         <v>1</v>
@@ -9102,7 +9102,7 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B259">
         <v>4</v>
@@ -9114,10 +9114,10 @@
         <v>20</v>
       </c>
       <c r="E259" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F259" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G259">
         <v>800</v>
@@ -9126,7 +9126,7 @@
         <v>0</v>
       </c>
       <c r="I259" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J259">
         <v>1</v>
@@ -9134,7 +9134,7 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B260">
         <v>4</v>
@@ -9146,10 +9146,10 @@
         <v>11</v>
       </c>
       <c r="E260" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F260" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G260">
         <v>200</v>
@@ -9158,7 +9158,7 @@
         <v>0</v>
       </c>
       <c r="I260" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J260">
         <v>1</v>
@@ -9166,7 +9166,7 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B261">
         <v>4</v>
@@ -9178,10 +9178,10 @@
         <v>20</v>
       </c>
       <c r="E261" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F261" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G261">
         <v>200</v>
@@ -9190,7 +9190,7 @@
         <v>0</v>
       </c>
       <c r="I261" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J261">
         <v>1</v>
@@ -9198,7 +9198,7 @@
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B262">
         <v>4</v>
@@ -9210,10 +9210,10 @@
         <v>11</v>
       </c>
       <c r="E262" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F262" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G262">
         <v>250</v>
@@ -9222,7 +9222,7 @@
         <v>0</v>
       </c>
       <c r="I262" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J262">
         <v>1</v>
@@ -9230,7 +9230,7 @@
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B263">
         <v>4</v>
@@ -9242,10 +9242,10 @@
         <v>20</v>
       </c>
       <c r="E263" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F263" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G263">
         <v>200</v>
@@ -9254,7 +9254,7 @@
         <v>0</v>
       </c>
       <c r="I263" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J263">
         <v>1</v>
@@ -9262,7 +9262,7 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B264">
         <v>6</v>
@@ -9274,10 +9274,10 @@
         <v>11</v>
       </c>
       <c r="E264" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F264" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G264">
         <v>250</v>
@@ -9286,7 +9286,7 @@
         <v>0</v>
       </c>
       <c r="I264" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J264">
         <v>1</v>
@@ -9294,7 +9294,7 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B265">
         <v>6</v>
@@ -9306,10 +9306,10 @@
         <v>20</v>
       </c>
       <c r="E265" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F265" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G265">
         <v>250</v>
@@ -9318,7 +9318,7 @@
         <v>0</v>
       </c>
       <c r="I265" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J265">
         <v>1</v>
@@ -9326,7 +9326,7 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B266">
         <v>3</v>
@@ -9338,10 +9338,10 @@
         <v>11</v>
       </c>
       <c r="E266" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F266" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G266">
         <v>300</v>
@@ -9350,7 +9350,7 @@
         <v>0</v>
       </c>
       <c r="I266" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J266">
         <v>1</v>
@@ -9358,7 +9358,7 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B267">
         <v>3</v>
@@ -9370,10 +9370,10 @@
         <v>20</v>
       </c>
       <c r="E267" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F267" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G267">
         <v>300</v>
@@ -9382,7 +9382,7 @@
         <v>0</v>
       </c>
       <c r="I267" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J267">
         <v>1</v>
@@ -9390,7 +9390,7 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B268">
         <v>8</v>
@@ -9402,10 +9402,10 @@
         <v>11</v>
       </c>
       <c r="E268" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F268" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G268">
         <v>500</v>
@@ -9414,7 +9414,7 @@
         <v>0</v>
       </c>
       <c r="I268" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J268">
         <v>1</v>
@@ -9422,7 +9422,7 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B269">
         <v>8</v>
@@ -9434,10 +9434,10 @@
         <v>20</v>
       </c>
       <c r="E269" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F269" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G269">
         <v>550</v>
@@ -9446,7 +9446,7 @@
         <v>0</v>
       </c>
       <c r="I269" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J269">
         <v>1</v>
@@ -9454,7 +9454,7 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B270">
         <v>2</v>
@@ -9466,10 +9466,10 @@
         <v>11</v>
       </c>
       <c r="E270" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F270" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G270">
         <v>500</v>
@@ -9478,7 +9478,7 @@
         <v>0</v>
       </c>
       <c r="I270" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J270">
         <v>1</v>
@@ -9486,7 +9486,7 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B271">
         <v>2</v>
@@ -9498,10 +9498,10 @@
         <v>20</v>
       </c>
       <c r="E271" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F271" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G271">
         <v>500</v>
@@ -9510,7 +9510,7 @@
         <v>0</v>
       </c>
       <c r="I271" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J271">
         <v>1</v>
@@ -9518,7 +9518,7 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B272">
         <v>14</v>
@@ -9530,10 +9530,10 @@
         <v>11</v>
       </c>
       <c r="E272" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F272" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G272">
         <v>550</v>
@@ -9550,7 +9550,7 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B273">
         <v>14</v>
@@ -9562,10 +9562,10 @@
         <v>20</v>
       </c>
       <c r="E273" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F273" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G273">
         <v>400</v>
@@ -9582,7 +9582,7 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B274">
         <v>14</v>
@@ -9594,10 +9594,10 @@
         <v>11</v>
       </c>
       <c r="E274" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F274" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G274">
         <v>550</v>
@@ -9614,7 +9614,7 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B275">
         <v>14</v>
@@ -9626,10 +9626,10 @@
         <v>20</v>
       </c>
       <c r="E275" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F275" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G275">
         <v>400</v>
@@ -9646,7 +9646,7 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B276">
         <v>14</v>
@@ -9658,10 +9658,10 @@
         <v>11</v>
       </c>
       <c r="E276" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F276" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G276">
         <v>300</v>
@@ -9678,7 +9678,7 @@
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B277">
         <v>14</v>
@@ -9690,10 +9690,10 @@
         <v>20</v>
       </c>
       <c r="E277" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F277" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G277">
         <v>300</v>
@@ -9710,7 +9710,7 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B278">
         <v>12</v>
@@ -9722,10 +9722,10 @@
         <v>11</v>
       </c>
       <c r="E278" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F278" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G278">
         <v>300</v>
@@ -9734,7 +9734,7 @@
         <v>0</v>
       </c>
       <c r="I278" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J278">
         <v>1</v>
@@ -9742,7 +9742,7 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B279">
         <v>12</v>
@@ -9754,10 +9754,10 @@
         <v>20</v>
       </c>
       <c r="E279" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F279" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G279">
         <v>350</v>
@@ -9766,7 +9766,7 @@
         <v>0</v>
       </c>
       <c r="I279" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J279">
         <v>1</v>
@@ -9774,7 +9774,7 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B280">
         <v>12</v>
@@ -9786,10 +9786,10 @@
         <v>11</v>
       </c>
       <c r="E280" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F280" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G280">
         <v>800</v>
@@ -9798,7 +9798,7 @@
         <v>0</v>
       </c>
       <c r="I280" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J280">
         <v>1</v>
@@ -9806,7 +9806,7 @@
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B281">
         <v>12</v>
@@ -9818,10 +9818,10 @@
         <v>20</v>
       </c>
       <c r="E281" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F281" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G281">
         <v>1000</v>
@@ -9830,7 +9830,7 @@
         <v>0</v>
       </c>
       <c r="I281" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J281">
         <v>1</v>
@@ -9838,7 +9838,7 @@
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B282">
         <v>12</v>
@@ -9850,10 +9850,10 @@
         <v>11</v>
       </c>
       <c r="E282" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F282" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G282">
         <v>300</v>
@@ -9862,7 +9862,7 @@
         <v>0</v>
       </c>
       <c r="I282" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J282">
         <v>1</v>
@@ -9870,7 +9870,7 @@
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B283">
         <v>12</v>
@@ -9882,10 +9882,10 @@
         <v>20</v>
       </c>
       <c r="E283" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F283" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G283">
         <v>300</v>
@@ -9894,7 +9894,7 @@
         <v>0</v>
       </c>
       <c r="I283" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J283">
         <v>1</v>
@@ -9902,7 +9902,7 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B284">
         <v>6</v>
@@ -9914,10 +9914,10 @@
         <v>11</v>
       </c>
       <c r="E284" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F284" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G284">
         <v>300</v>
@@ -9926,7 +9926,7 @@
         <v>0</v>
       </c>
       <c r="I284" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J284">
         <v>1</v>
@@ -9934,7 +9934,7 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B285">
         <v>6</v>
@@ -9946,10 +9946,10 @@
         <v>20</v>
       </c>
       <c r="E285" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F285" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G285">
         <v>300</v>
@@ -9958,7 +9958,7 @@
         <v>0</v>
       </c>
       <c r="I285" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J285">
         <v>1</v>
@@ -9966,7 +9966,7 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B286">
         <v>8</v>
@@ -9978,10 +9978,10 @@
         <v>11</v>
       </c>
       <c r="E286" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F286" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G286">
         <v>850</v>
@@ -9990,7 +9990,7 @@
         <v>0</v>
       </c>
       <c r="I286" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J286">
         <v>1</v>
@@ -9998,7 +9998,7 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B287">
         <v>8</v>
@@ -10010,10 +10010,10 @@
         <v>20</v>
       </c>
       <c r="E287" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F287" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G287">
         <v>850</v>
@@ -10022,7 +10022,7 @@
         <v>0</v>
       </c>
       <c r="I287" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J287">
         <v>1</v>
@@ -10030,7 +10030,7 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B288">
         <v>8</v>
@@ -10042,10 +10042,10 @@
         <v>11</v>
       </c>
       <c r="E288" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F288" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G288">
         <v>850</v>
@@ -10054,7 +10054,7 @@
         <v>0</v>
       </c>
       <c r="I288" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J288">
         <v>1</v>
@@ -10062,7 +10062,7 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B289">
         <v>8</v>
@@ -10074,10 +10074,10 @@
         <v>20</v>
       </c>
       <c r="E289" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F289" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G289">
         <v>850</v>
@@ -10086,7 +10086,7 @@
         <v>0</v>
       </c>
       <c r="I289" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J289">
         <v>1</v>
@@ -10094,7 +10094,7 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B290">
         <v>8</v>
@@ -10106,10 +10106,10 @@
         <v>11</v>
       </c>
       <c r="E290" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F290" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G290">
         <v>850</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="I290" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J290">
         <v>1</v>
@@ -10126,7 +10126,7 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B291">
         <v>8</v>
@@ -10138,10 +10138,10 @@
         <v>20</v>
       </c>
       <c r="E291" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F291" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G291">
         <v>850</v>
@@ -10150,7 +10150,7 @@
         <v>0</v>
       </c>
       <c r="I291" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J291">
         <v>1</v>
@@ -10158,7 +10158,7 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B292">
         <v>12</v>
@@ -10170,10 +10170,10 @@
         <v>11</v>
       </c>
       <c r="E292" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F292" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G292">
         <v>1000</v>
@@ -10182,7 +10182,7 @@
         <v>0</v>
       </c>
       <c r="I292" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J292">
         <v>2</v>
@@ -10190,7 +10190,7 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B293">
         <v>12</v>
@@ -10202,10 +10202,10 @@
         <v>20</v>
       </c>
       <c r="E293" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F293" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G293">
         <v>1000</v>
@@ -10214,7 +10214,7 @@
         <v>0</v>
       </c>
       <c r="I293" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J293">
         <v>2</v>
@@ -10222,7 +10222,7 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B294">
         <v>12</v>
@@ -10234,10 +10234,10 @@
         <v>11</v>
       </c>
       <c r="E294" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F294" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G294">
         <v>1000</v>
@@ -10246,7 +10246,7 @@
         <v>0</v>
       </c>
       <c r="I294" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J294">
         <v>2</v>
@@ -10254,7 +10254,7 @@
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B295">
         <v>12</v>
@@ -10266,10 +10266,10 @@
         <v>20</v>
       </c>
       <c r="E295" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F295" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G295">
         <v>1000</v>
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="I295" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J295">
         <v>2</v>
@@ -10286,7 +10286,7 @@
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B296">
         <v>12</v>
@@ -10298,10 +10298,10 @@
         <v>11</v>
       </c>
       <c r="E296" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F296" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G296">
         <v>100</v>
@@ -10310,7 +10310,7 @@
         <v>0</v>
       </c>
       <c r="I296" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J296">
         <v>2</v>
@@ -10318,7 +10318,7 @@
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B297">
         <v>12</v>
@@ -10330,10 +10330,10 @@
         <v>20</v>
       </c>
       <c r="E297" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F297" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G297">
         <v>100</v>
@@ -10342,7 +10342,7 @@
         <v>0</v>
       </c>
       <c r="I297" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J297">
         <v>2</v>
@@ -10350,22 +10350,22 @@
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B298">
+        <v>20</v>
+      </c>
+      <c r="C298" t="s">
+        <v>10</v>
+      </c>
+      <c r="D298" t="s">
+        <v>11</v>
+      </c>
+      <c r="E298" t="s">
         <v>186</v>
       </c>
-      <c r="B298">
-        <v>20</v>
-      </c>
-      <c r="C298" t="s">
-        <v>10</v>
-      </c>
-      <c r="D298" t="s">
-        <v>11</v>
-      </c>
-      <c r="E298" t="s">
-        <v>187</v>
-      </c>
       <c r="F298" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G298">
         <v>750</v>
@@ -10374,7 +10374,7 @@
         <v>0</v>
       </c>
       <c r="I298" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J298">
         <v>1</v>
@@ -10382,22 +10382,22 @@
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B299">
+        <v>20</v>
+      </c>
+      <c r="C299" t="s">
+        <v>10</v>
+      </c>
+      <c r="D299" t="s">
+        <v>20</v>
+      </c>
+      <c r="E299" t="s">
         <v>186</v>
       </c>
-      <c r="B299">
-        <v>20</v>
-      </c>
-      <c r="C299" t="s">
-        <v>10</v>
-      </c>
-      <c r="D299" t="s">
-        <v>20</v>
-      </c>
-      <c r="E299" t="s">
-        <v>187</v>
-      </c>
       <c r="F299" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G299">
         <v>750</v>
@@ -10406,7 +10406,7 @@
         <v>0</v>
       </c>
       <c r="I299" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J299">
         <v>1</v>
@@ -10414,7 +10414,7 @@
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B300">
         <v>12</v>
@@ -10426,10 +10426,10 @@
         <v>11</v>
       </c>
       <c r="E300" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F300" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G300">
         <v>500</v>
@@ -10438,7 +10438,7 @@
         <v>0</v>
       </c>
       <c r="I300" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J300">
         <v>1</v>
@@ -10446,7 +10446,7 @@
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B301">
         <v>12</v>
@@ -10458,10 +10458,10 @@
         <v>20</v>
       </c>
       <c r="E301" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F301" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G301">
         <v>650</v>
@@ -10470,7 +10470,7 @@
         <v>0</v>
       </c>
       <c r="I301" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J301">
         <v>1</v>
@@ -10478,7 +10478,7 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B302">
         <v>7</v>
@@ -10490,10 +10490,10 @@
         <v>11</v>
       </c>
       <c r="E302" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F302" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G302">
         <v>1000</v>
@@ -10502,7 +10502,7 @@
         <v>0</v>
       </c>
       <c r="I302" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J302">
         <v>1</v>
@@ -10510,7 +10510,7 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B303">
         <v>7</v>
@@ -10522,10 +10522,10 @@
         <v>20</v>
       </c>
       <c r="E303" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F303" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G303">
         <v>950</v>
@@ -10534,7 +10534,7 @@
         <v>0</v>
       </c>
       <c r="I303" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J303">
         <v>1</v>
@@ -10542,7 +10542,7 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B304">
         <v>7</v>
@@ -10554,10 +10554,10 @@
         <v>11</v>
       </c>
       <c r="E304" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F304" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G304">
         <v>1000</v>
@@ -10566,7 +10566,7 @@
         <v>0</v>
       </c>
       <c r="I304" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J304">
         <v>1</v>
@@ -10574,7 +10574,7 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B305">
         <v>7</v>
@@ -10586,10 +10586,10 @@
         <v>20</v>
       </c>
       <c r="E305" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F305" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G305">
         <v>750</v>
@@ -10598,7 +10598,7 @@
         <v>0</v>
       </c>
       <c r="I305" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J305">
         <v>1</v>
@@ -10606,7 +10606,7 @@
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B306">
         <v>7</v>
@@ -10618,10 +10618,10 @@
         <v>11</v>
       </c>
       <c r="E306" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F306" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G306">
         <v>250</v>
@@ -10630,7 +10630,7 @@
         <v>0</v>
       </c>
       <c r="I306" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J306">
         <v>1</v>
@@ -10638,7 +10638,7 @@
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B307">
         <v>7</v>
@@ -10650,10 +10650,10 @@
         <v>20</v>
       </c>
       <c r="E307" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F307" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G307">
         <v>250</v>
@@ -10662,7 +10662,7 @@
         <v>0</v>
       </c>
       <c r="I307" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J307">
         <v>1</v>
@@ -10670,7 +10670,7 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B308">
         <v>7</v>
@@ -10682,10 +10682,10 @@
         <v>11</v>
       </c>
       <c r="E308" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F308" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G308">
         <v>500</v>
@@ -10694,7 +10694,7 @@
         <v>0</v>
       </c>
       <c r="I308" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J308">
         <v>1</v>
@@ -10702,7 +10702,7 @@
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B309">
         <v>7</v>
@@ -10714,10 +10714,10 @@
         <v>20</v>
       </c>
       <c r="E309" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F309" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G309">
         <v>1000</v>
@@ -10726,7 +10726,7 @@
         <v>0</v>
       </c>
       <c r="I309" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J309">
         <v>1</v>
@@ -10734,7 +10734,7 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B310">
         <v>7</v>
@@ -10746,10 +10746,10 @@
         <v>11</v>
       </c>
       <c r="E310" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F310" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G310">
         <v>700</v>
@@ -10758,7 +10758,7 @@
         <v>0</v>
       </c>
       <c r="I310" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J310">
         <v>1</v>
@@ -10766,7 +10766,7 @@
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B311">
         <v>7</v>
@@ -10778,10 +10778,10 @@
         <v>20</v>
       </c>
       <c r="E311" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F311" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G311">
         <v>500</v>
@@ -10790,7 +10790,7 @@
         <v>0</v>
       </c>
       <c r="I311" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J311">
         <v>1</v>
@@ -10798,7 +10798,7 @@
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B312">
         <v>7</v>
@@ -10810,10 +10810,10 @@
         <v>11</v>
       </c>
       <c r="E312" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F312" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G312">
         <v>100</v>
@@ -10822,7 +10822,7 @@
         <v>0</v>
       </c>
       <c r="I312" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J312">
         <v>1</v>
@@ -10830,7 +10830,7 @@
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B313">
         <v>7</v>
@@ -10842,10 +10842,10 @@
         <v>20</v>
       </c>
       <c r="E313" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F313" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G313">
         <v>100</v>
@@ -10854,7 +10854,7 @@
         <v>0</v>
       </c>
       <c r="I313" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J313">
         <v>1</v>
@@ -10862,7 +10862,7 @@
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B314">
         <v>15</v>
@@ -10874,10 +10874,10 @@
         <v>11</v>
       </c>
       <c r="E314" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F314" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G314">
         <v>150</v>
@@ -10886,7 +10886,7 @@
         <v>0</v>
       </c>
       <c r="I314" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J314">
         <v>1</v>
@@ -10894,7 +10894,7 @@
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B315">
         <v>15</v>
@@ -10906,10 +10906,10 @@
         <v>20</v>
       </c>
       <c r="E315" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F315" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G315">
         <v>200</v>
@@ -10918,7 +10918,7 @@
         <v>0</v>
       </c>
       <c r="I315" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J315">
         <v>1</v>
@@ -10926,7 +10926,7 @@
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B316">
         <v>6</v>
@@ -10938,10 +10938,10 @@
         <v>11</v>
       </c>
       <c r="E316" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F316" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G316">
         <v>500</v>
@@ -10950,7 +10950,7 @@
         <v>0</v>
       </c>
       <c r="I316" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J316">
         <v>1</v>
@@ -10958,7 +10958,7 @@
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B317">
         <v>6</v>
@@ -10970,10 +10970,10 @@
         <v>20</v>
       </c>
       <c r="E317" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F317" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G317">
         <v>500</v>
@@ -10982,7 +10982,7 @@
         <v>0</v>
       </c>
       <c r="I317" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J317">
         <v>1</v>
@@ -10990,7 +10990,7 @@
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B318">
         <v>6</v>
@@ -11002,10 +11002,10 @@
         <v>11</v>
       </c>
       <c r="E318" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F318" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G318">
         <v>500</v>
@@ -11014,7 +11014,7 @@
         <v>0</v>
       </c>
       <c r="I318" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J318">
         <v>1</v>
@@ -11022,7 +11022,7 @@
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B319">
         <v>6</v>
@@ -11034,10 +11034,10 @@
         <v>20</v>
       </c>
       <c r="E319" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F319" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G319">
         <v>500</v>
@@ -11046,7 +11046,7 @@
         <v>0</v>
       </c>
       <c r="I319" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J319">
         <v>1</v>
@@ -11054,7 +11054,7 @@
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B320">
         <v>6</v>
@@ -11066,10 +11066,10 @@
         <v>11</v>
       </c>
       <c r="E320" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F320" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G320">
         <v>500</v>
@@ -11078,7 +11078,7 @@
         <v>0</v>
       </c>
       <c r="I320" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J320">
         <v>1</v>
@@ -11086,7 +11086,7 @@
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B321">
         <v>6</v>
@@ -11098,10 +11098,10 @@
         <v>20</v>
       </c>
       <c r="E321" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F321" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G321">
         <v>500</v>
@@ -11110,7 +11110,7 @@
         <v>0</v>
       </c>
       <c r="I321" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J321">
         <v>1</v>
@@ -11118,7 +11118,7 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B322">
         <v>9</v>
@@ -11130,10 +11130,10 @@
         <v>11</v>
       </c>
       <c r="E322" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F322" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G322">
         <v>750</v>
@@ -11142,7 +11142,7 @@
         <v>0</v>
       </c>
       <c r="I322" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J322">
         <v>1</v>
@@ -11150,7 +11150,7 @@
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B323">
         <v>9</v>
@@ -11162,10 +11162,10 @@
         <v>20</v>
       </c>
       <c r="E323" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F323" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G323">
         <v>750</v>
@@ -11174,7 +11174,7 @@
         <v>0</v>
       </c>
       <c r="I323" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J323">
         <v>1</v>
@@ -11182,7 +11182,7 @@
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B324">
         <v>4</v>
@@ -11194,10 +11194,10 @@
         <v>11</v>
       </c>
       <c r="E324" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F324" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G324">
         <v>200</v>
@@ -11206,7 +11206,7 @@
         <v>0</v>
       </c>
       <c r="I324" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J324">
         <v>1</v>
@@ -11214,7 +11214,7 @@
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B325">
         <v>4</v>
@@ -11226,10 +11226,10 @@
         <v>20</v>
       </c>
       <c r="E325" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F325" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G325">
         <v>200</v>
@@ -11238,7 +11238,7 @@
         <v>0</v>
       </c>
       <c r="I325" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J325">
         <v>1</v>
@@ -11246,7 +11246,7 @@
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B326">
         <v>4</v>
@@ -11258,10 +11258,10 @@
         <v>11</v>
       </c>
       <c r="E326" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F326" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G326">
         <v>200</v>
@@ -11270,7 +11270,7 @@
         <v>0</v>
       </c>
       <c r="I326" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J326">
         <v>1</v>
@@ -11278,7 +11278,7 @@
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B327">
         <v>4</v>
@@ -11290,10 +11290,10 @@
         <v>20</v>
       </c>
       <c r="E327" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F327" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G327">
         <v>300</v>
@@ -11302,7 +11302,7 @@
         <v>0</v>
       </c>
       <c r="I327" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J327">
         <v>1</v>
@@ -11310,7 +11310,7 @@
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B328">
         <v>4</v>
@@ -11322,10 +11322,10 @@
         <v>11</v>
       </c>
       <c r="E328" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F328" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G328">
         <v>200</v>
@@ -11334,7 +11334,7 @@
         <v>0</v>
       </c>
       <c r="I328" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J328">
         <v>1</v>
@@ -11342,7 +11342,7 @@
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B329">
         <v>4</v>
@@ -11354,10 +11354,10 @@
         <v>20</v>
       </c>
       <c r="E329" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F329" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G329">
         <v>200</v>
@@ -11366,7 +11366,7 @@
         <v>0</v>
       </c>
       <c r="I329" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J329">
         <v>1</v>
@@ -11374,7 +11374,7 @@
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B330">
         <v>12</v>
@@ -11386,10 +11386,10 @@
         <v>11</v>
       </c>
       <c r="E330" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F330" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G330">
         <v>950</v>
@@ -11398,7 +11398,7 @@
         <v>0</v>
       </c>
       <c r="I330" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J330">
         <v>1</v>
@@ -11406,7 +11406,7 @@
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B331">
         <v>12</v>
@@ -11418,10 +11418,10 @@
         <v>20</v>
       </c>
       <c r="E331" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F331" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G331">
         <v>1000</v>
@@ -11430,7 +11430,7 @@
         <v>0</v>
       </c>
       <c r="I331" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J331">
         <v>1</v>
@@ -11438,7 +11438,7 @@
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B332">
         <v>3</v>
@@ -11450,10 +11450,10 @@
         <v>11</v>
       </c>
       <c r="E332" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F332" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G332">
         <v>1000</v>
@@ -11462,7 +11462,7 @@
         <v>0</v>
       </c>
       <c r="I332" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J332">
         <v>2</v>
@@ -11470,7 +11470,7 @@
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B333">
         <v>3</v>
@@ -11482,10 +11482,10 @@
         <v>20</v>
       </c>
       <c r="E333" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F333" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G333">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
         <v>0</v>
       </c>
       <c r="I333" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J333">
         <v>2</v>
@@ -11502,22 +11502,22 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B334">
+        <v>10</v>
+      </c>
+      <c r="C334" t="s">
+        <v>10</v>
+      </c>
+      <c r="D334" t="s">
+        <v>11</v>
+      </c>
+      <c r="E334" t="s">
         <v>209</v>
       </c>
-      <c r="B334">
-        <v>10</v>
-      </c>
-      <c r="C334" t="s">
-        <v>10</v>
-      </c>
-      <c r="D334" t="s">
-        <v>11</v>
-      </c>
-      <c r="E334" t="s">
-        <v>210</v>
-      </c>
       <c r="F334" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G334">
         <v>300</v>
@@ -11526,7 +11526,7 @@
         <v>0</v>
       </c>
       <c r="I334" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J334">
         <v>1</v>
@@ -11534,22 +11534,22 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B335">
+        <v>10</v>
+      </c>
+      <c r="C335" t="s">
+        <v>10</v>
+      </c>
+      <c r="D335" t="s">
+        <v>20</v>
+      </c>
+      <c r="E335" t="s">
         <v>209</v>
       </c>
-      <c r="B335">
-        <v>10</v>
-      </c>
-      <c r="C335" t="s">
-        <v>10</v>
-      </c>
-      <c r="D335" t="s">
-        <v>20</v>
-      </c>
-      <c r="E335" t="s">
-        <v>210</v>
-      </c>
       <c r="F335" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G335">
         <v>300</v>
@@ -11558,7 +11558,7 @@
         <v>0</v>
       </c>
       <c r="I335" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J335">
         <v>1</v>
@@ -11566,7 +11566,7 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B336">
         <v>10</v>
@@ -11578,10 +11578,10 @@
         <v>11</v>
       </c>
       <c r="E336" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F336" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G336">
         <v>300</v>
@@ -11590,7 +11590,7 @@
         <v>0</v>
       </c>
       <c r="I336" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J336">
         <v>1</v>
@@ -11598,7 +11598,7 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B337">
         <v>10</v>
@@ -11610,10 +11610,10 @@
         <v>20</v>
       </c>
       <c r="E337" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F337" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G337">
         <v>300</v>
@@ -11622,7 +11622,7 @@
         <v>0</v>
       </c>
       <c r="I337" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J337">
         <v>1</v>
@@ -11630,7 +11630,7 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B338">
         <v>10</v>
@@ -11642,10 +11642,10 @@
         <v>11</v>
       </c>
       <c r="E338" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F338" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G338">
         <v>750</v>
@@ -11654,7 +11654,7 @@
         <v>0</v>
       </c>
       <c r="I338" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J338">
         <v>1</v>
@@ -11662,7 +11662,7 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B339">
         <v>10</v>
@@ -11674,10 +11674,10 @@
         <v>20</v>
       </c>
       <c r="E339" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F339" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G339">
         <v>750</v>
@@ -11686,7 +11686,7 @@
         <v>0</v>
       </c>
       <c r="I339" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J339">
         <v>1</v>
@@ -11694,7 +11694,7 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B340">
         <v>3</v>
@@ -11706,10 +11706,10 @@
         <v>11</v>
       </c>
       <c r="E340" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F340" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G340">
         <v>500</v>
@@ -11718,7 +11718,7 @@
         <v>0</v>
       </c>
       <c r="I340" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J340">
         <v>1</v>
@@ -11726,7 +11726,7 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B341">
         <v>3</v>
@@ -11738,10 +11738,10 @@
         <v>20</v>
       </c>
       <c r="E341" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F341" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G341">
         <v>500</v>
@@ -11750,7 +11750,7 @@
         <v>0</v>
       </c>
       <c r="I341" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J341">
         <v>1</v>
@@ -11758,7 +11758,7 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B342">
         <v>12</v>
@@ -11770,10 +11770,10 @@
         <v>11</v>
       </c>
       <c r="E342" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F342" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G342">
         <v>300</v>
@@ -11790,7 +11790,7 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B343">
         <v>12</v>
@@ -11802,10 +11802,10 @@
         <v>20</v>
       </c>
       <c r="E343" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F343" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G343">
         <v>250</v>
@@ -11822,7 +11822,7 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B344">
         <v>12</v>
@@ -11834,10 +11834,10 @@
         <v>11</v>
       </c>
       <c r="E344" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F344" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G344">
         <v>250</v>
@@ -11854,7 +11854,7 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B345">
         <v>12</v>
@@ -11866,10 +11866,10 @@
         <v>20</v>
       </c>
       <c r="E345" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F345" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G345">
         <v>250</v>
@@ -11886,7 +11886,7 @@
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B346">
         <v>12</v>
@@ -11898,10 +11898,10 @@
         <v>11</v>
       </c>
       <c r="E346" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F346" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G346">
         <v>800</v>
@@ -11918,7 +11918,7 @@
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B347">
         <v>12</v>
@@ -11930,10 +11930,10 @@
         <v>20</v>
       </c>
       <c r="E347" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F347" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G347">
         <v>800</v>
@@ -11950,7 +11950,7 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B348">
         <v>2</v>
@@ -11962,10 +11962,10 @@
         <v>11</v>
       </c>
       <c r="E348" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F348" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G348">
         <v>250</v>
@@ -11982,7 +11982,7 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B349">
         <v>2</v>
@@ -11994,10 +11994,10 @@
         <v>20</v>
       </c>
       <c r="E349" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F349" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G349">
         <v>250</v>
@@ -12014,7 +12014,7 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B350">
         <v>2</v>
@@ -12026,10 +12026,10 @@
         <v>11</v>
       </c>
       <c r="E350" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F350" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G350">
         <v>250</v>
@@ -12046,7 +12046,7 @@
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B351">
         <v>2</v>
@@ -12058,10 +12058,10 @@
         <v>20</v>
       </c>
       <c r="E351" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F351" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G351">
         <v>250</v>
@@ -12078,7 +12078,7 @@
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B352">
         <v>2</v>
@@ -12090,10 +12090,10 @@
         <v>11</v>
       </c>
       <c r="E352" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F352" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G352">
         <v>250</v>
@@ -12110,7 +12110,7 @@
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B353">
         <v>2</v>
@@ -12122,10 +12122,10 @@
         <v>20</v>
       </c>
       <c r="E353" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F353" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G353">
         <v>250</v>
@@ -12142,7 +12142,7 @@
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B354">
         <v>2</v>
@@ -12154,10 +12154,10 @@
         <v>11</v>
       </c>
       <c r="E354" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F354" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G354">
         <v>200</v>
@@ -12174,7 +12174,7 @@
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B355">
         <v>2</v>
@@ -12186,10 +12186,10 @@
         <v>20</v>
       </c>
       <c r="E355" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F355" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G355">
         <v>200</v>
@@ -12206,7 +12206,7 @@
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B356">
         <v>2</v>
@@ -12218,10 +12218,10 @@
         <v>11</v>
       </c>
       <c r="E356" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F356" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G356">
         <v>200</v>
@@ -12238,7 +12238,7 @@
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B357">
         <v>2</v>
@@ -12250,10 +12250,10 @@
         <v>20</v>
       </c>
       <c r="E357" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F357" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G357">
         <v>200</v>
@@ -12270,7 +12270,7 @@
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B358">
         <v>2</v>
@@ -12282,10 +12282,10 @@
         <v>11</v>
       </c>
       <c r="E358" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F358" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G358">
         <v>200</v>
@@ -12302,7 +12302,7 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B359">
         <v>2</v>
@@ -12314,10 +12314,10 @@
         <v>20</v>
       </c>
       <c r="E359" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F359" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G359">
         <v>200</v>
@@ -12334,7 +12334,7 @@
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B360">
         <v>8</v>
@@ -12346,10 +12346,10 @@
         <v>11</v>
       </c>
       <c r="E360" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F360" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G360">
         <v>250</v>
@@ -12366,7 +12366,7 @@
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B361">
         <v>8</v>
@@ -12378,10 +12378,10 @@
         <v>20</v>
       </c>
       <c r="E361" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F361" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G361">
         <v>250</v>
@@ -12398,7 +12398,7 @@
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B362">
         <v>8</v>
@@ -12410,10 +12410,10 @@
         <v>11</v>
       </c>
       <c r="E362" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F362" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G362">
         <v>250</v>
@@ -12430,7 +12430,7 @@
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B363">
         <v>8</v>
@@ -12442,10 +12442,10 @@
         <v>20</v>
       </c>
       <c r="E363" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F363" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G363">
         <v>250</v>
@@ -12462,7 +12462,7 @@
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B364">
         <v>8</v>
@@ -12474,10 +12474,10 @@
         <v>11</v>
       </c>
       <c r="E364" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F364" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G364">
         <v>250</v>
@@ -12494,7 +12494,7 @@
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B365">
         <v>8</v>
@@ -12506,10 +12506,10 @@
         <v>20</v>
       </c>
       <c r="E365" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F365" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G365">
         <v>250</v>
@@ -12526,7 +12526,7 @@
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B366">
         <v>16</v>
@@ -12538,10 +12538,10 @@
         <v>11</v>
       </c>
       <c r="E366" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F366" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G366">
         <v>150</v>
@@ -12558,7 +12558,7 @@
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B367">
         <v>16</v>
@@ -12570,10 +12570,10 @@
         <v>20</v>
       </c>
       <c r="E367" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F367" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G367">
         <v>150</v>
@@ -12590,7 +12590,7 @@
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B368">
         <v>2</v>
@@ -12602,10 +12602,10 @@
         <v>11</v>
       </c>
       <c r="E368" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F368" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G368">
         <v>550</v>
@@ -12614,7 +12614,7 @@
         <v>0</v>
       </c>
       <c r="I368" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J368">
         <v>1</v>
@@ -12622,7 +12622,7 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B369">
         <v>2</v>
@@ -12634,10 +12634,10 @@
         <v>20</v>
       </c>
       <c r="E369" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F369" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G369">
         <v>550</v>
@@ -12646,7 +12646,7 @@
         <v>0</v>
       </c>
       <c r="I369" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J369">
         <v>1</v>
@@ -12654,7 +12654,7 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B370">
         <v>17</v>
@@ -12666,10 +12666,10 @@
         <v>11</v>
       </c>
       <c r="E370" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F370" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G370">
         <v>800</v>
@@ -12678,7 +12678,7 @@
         <v>0</v>
       </c>
       <c r="I370" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J370">
         <v>1</v>
@@ -12686,7 +12686,7 @@
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B371">
         <v>17</v>
@@ -12698,10 +12698,10 @@
         <v>20</v>
       </c>
       <c r="E371" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F371" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G371">
         <v>800</v>
@@ -12710,7 +12710,7 @@
         <v>0</v>
       </c>
       <c r="I371" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J371">
         <v>1</v>
@@ -12718,7 +12718,7 @@
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B372">
         <v>17</v>
@@ -12730,10 +12730,10 @@
         <v>11</v>
       </c>
       <c r="E372" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F372" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G372">
         <v>800</v>
@@ -12742,7 +12742,7 @@
         <v>0</v>
       </c>
       <c r="I372" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J372">
         <v>1</v>
@@ -12750,7 +12750,7 @@
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B373">
         <v>17</v>
@@ -12762,10 +12762,10 @@
         <v>20</v>
       </c>
       <c r="E373" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F373" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G373">
         <v>800</v>
@@ -12774,7 +12774,7 @@
         <v>0</v>
       </c>
       <c r="I373" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J373">
         <v>1</v>
@@ -12782,7 +12782,7 @@
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B374">
         <v>17</v>
@@ -12794,10 +12794,10 @@
         <v>11</v>
       </c>
       <c r="E374" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F374" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G374">
         <v>300</v>
@@ -12806,7 +12806,7 @@
         <v>0</v>
       </c>
       <c r="I374" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J374">
         <v>1</v>
@@ -12814,7 +12814,7 @@
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B375">
         <v>17</v>
@@ -12826,10 +12826,10 @@
         <v>20</v>
       </c>
       <c r="E375" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F375" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G375">
         <v>300</v>
@@ -12838,7 +12838,7 @@
         <v>0</v>
       </c>
       <c r="I375" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J375">
         <v>1</v>
@@ -12846,7 +12846,7 @@
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B376">
         <v>1</v>
@@ -12858,10 +12858,10 @@
         <v>11</v>
       </c>
       <c r="E376" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F376" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G376">
         <v>100</v>
@@ -12870,7 +12870,7 @@
         <v>0</v>
       </c>
       <c r="I376" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J376">
         <v>1</v>
@@ -12878,7 +12878,7 @@
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B377">
         <v>1</v>
@@ -12890,10 +12890,10 @@
         <v>20</v>
       </c>
       <c r="E377" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F377" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G377">
         <v>101</v>
@@ -12902,7 +12902,7 @@
         <v>0</v>
       </c>
       <c r="I377" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J377">
         <v>1</v>
@@ -12910,7 +12910,7 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B378">
         <v>1</v>
@@ -12922,10 +12922,10 @@
         <v>20</v>
       </c>
       <c r="E378" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F378" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G378">
         <v>150</v>
@@ -12934,7 +12934,7 @@
         <v>0</v>
       </c>
       <c r="I378" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J378">
         <v>1</v>
@@ -12942,7 +12942,7 @@
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B379">
         <v>1</v>
@@ -12954,10 +12954,10 @@
         <v>11</v>
       </c>
       <c r="E379" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F379" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G379">
         <v>100</v>
@@ -12966,7 +12966,7 @@
         <v>0</v>
       </c>
       <c r="I379" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J379">
         <v>1</v>
@@ -12974,22 +12974,22 @@
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B380">
+        <v>1</v>
+      </c>
+      <c r="C380" t="s">
+        <v>10</v>
+      </c>
+      <c r="D380" t="s">
+        <v>20</v>
+      </c>
+      <c r="E380" t="s">
         <v>228</v>
       </c>
-      <c r="B380">
-        <v>1</v>
-      </c>
-      <c r="C380" t="s">
-        <v>10</v>
-      </c>
-      <c r="D380" t="s">
-        <v>20</v>
-      </c>
-      <c r="E380" t="s">
-        <v>229</v>
-      </c>
       <c r="F380" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G380">
         <v>100</v>
@@ -12998,7 +12998,7 @@
         <v>0</v>
       </c>
       <c r="I380" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J380">
         <v>1</v>
@@ -13006,22 +13006,22 @@
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B381">
+        <v>1</v>
+      </c>
+      <c r="C381" t="s">
+        <v>10</v>
+      </c>
+      <c r="D381" t="s">
+        <v>11</v>
+      </c>
+      <c r="E381" t="s">
         <v>228</v>
       </c>
-      <c r="B381">
-        <v>1</v>
-      </c>
-      <c r="C381" t="s">
-        <v>10</v>
-      </c>
-      <c r="D381" t="s">
-        <v>11</v>
-      </c>
-      <c r="E381" t="s">
-        <v>229</v>
-      </c>
       <c r="F381" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G381">
         <v>100</v>
@@ -13030,7 +13030,7 @@
         <v>0</v>
       </c>
       <c r="I381" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J381">
         <v>1</v>
@@ -13038,7 +13038,7 @@
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B382">
         <v>21</v>
@@ -13050,10 +13050,10 @@
         <v>11</v>
       </c>
       <c r="E382" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F382" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G382">
         <v>125</v>
@@ -13062,7 +13062,7 @@
         <v>0</v>
       </c>
       <c r="I382" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J382">
         <v>1</v>
@@ -13070,7 +13070,7 @@
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B383">
         <v>21</v>
@@ -13082,10 +13082,10 @@
         <v>20</v>
       </c>
       <c r="E383" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F383" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G383">
         <v>205</v>
@@ -13094,7 +13094,7 @@
         <v>0</v>
       </c>
       <c r="I383" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J383">
         <v>1</v>
@@ -13102,7 +13102,7 @@
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B384">
         <v>11</v>
@@ -13114,10 +13114,10 @@
         <v>11</v>
       </c>
       <c r="E384" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F384" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G384">
         <v>120</v>
@@ -13126,7 +13126,7 @@
         <v>0</v>
       </c>
       <c r="I384" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J384">
         <v>1</v>
@@ -13134,7 +13134,7 @@
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B385">
         <v>11</v>
@@ -13146,10 +13146,10 @@
         <v>20</v>
       </c>
       <c r="E385" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F385" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G385">
         <v>100</v>
@@ -13158,7 +13158,7 @@
         <v>0</v>
       </c>
       <c r="I385" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J385">
         <v>1</v>
@@ -13166,22 +13166,22 @@
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B386">
+        <v>11</v>
+      </c>
+      <c r="C386" t="s">
+        <v>10</v>
+      </c>
+      <c r="D386" t="s">
+        <v>11</v>
+      </c>
+      <c r="E386" t="s">
         <v>233</v>
       </c>
-      <c r="B386">
-        <v>11</v>
-      </c>
-      <c r="C386" t="s">
-        <v>10</v>
-      </c>
-      <c r="D386" t="s">
-        <v>11</v>
-      </c>
-      <c r="E386" t="s">
-        <v>234</v>
-      </c>
       <c r="F386" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G386">
         <v>200</v>
@@ -13190,7 +13190,7 @@
         <v>0</v>
       </c>
       <c r="I386" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J386">
         <v>1</v>
@@ -13198,22 +13198,22 @@
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B387">
+        <v>11</v>
+      </c>
+      <c r="C387" t="s">
+        <v>10</v>
+      </c>
+      <c r="D387" t="s">
+        <v>20</v>
+      </c>
+      <c r="E387" t="s">
         <v>233</v>
       </c>
-      <c r="B387">
-        <v>11</v>
-      </c>
-      <c r="C387" t="s">
-        <v>10</v>
-      </c>
-      <c r="D387" t="s">
-        <v>20</v>
-      </c>
-      <c r="E387" t="s">
-        <v>234</v>
-      </c>
       <c r="F387" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G387">
         <v>200</v>
@@ -13222,7 +13222,7 @@
         <v>0</v>
       </c>
       <c r="I387" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J387">
         <v>1</v>
@@ -13230,7 +13230,7 @@
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B388">
         <v>11</v>
@@ -13242,10 +13242,10 @@
         <v>11</v>
       </c>
       <c r="E388" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F388" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G388">
         <v>200</v>
@@ -13254,7 +13254,7 @@
         <v>0</v>
       </c>
       <c r="I388" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J388">
         <v>1</v>
@@ -13262,7 +13262,7 @@
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B389">
         <v>11</v>
@@ -13274,10 +13274,10 @@
         <v>20</v>
       </c>
       <c r="E389" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F389" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G389">
         <v>200</v>
@@ -13286,7 +13286,7 @@
         <v>0</v>
       </c>
       <c r="I389" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J389">
         <v>1</v>
@@ -13294,7 +13294,7 @@
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B390">
         <v>12</v>
@@ -13306,10 +13306,10 @@
         <v>11</v>
       </c>
       <c r="E390" t="s">
+        <v>236</v>
+      </c>
+      <c r="F390" t="s">
         <v>237</v>
-      </c>
-      <c r="F390" t="s">
-        <v>238</v>
       </c>
       <c r="G390">
         <v>160</v>
@@ -13318,7 +13318,7 @@
         <v>0</v>
       </c>
       <c r="I390" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J390">
         <v>1</v>
@@ -13326,7 +13326,7 @@
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B391">
         <v>12</v>
@@ -13338,10 +13338,10 @@
         <v>20</v>
       </c>
       <c r="E391" t="s">
+        <v>236</v>
+      </c>
+      <c r="F391" t="s">
         <v>237</v>
-      </c>
-      <c r="F391" t="s">
-        <v>238</v>
       </c>
       <c r="G391">
         <v>245</v>
@@ -13350,7 +13350,7 @@
         <v>0</v>
       </c>
       <c r="I391" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J391">
         <v>1</v>
@@ -13358,7 +13358,7 @@
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B392">
         <v>7</v>
@@ -13370,10 +13370,10 @@
         <v>11</v>
       </c>
       <c r="E392" t="s">
+        <v>239</v>
+      </c>
+      <c r="F392" t="s">
         <v>240</v>
-      </c>
-      <c r="F392" t="s">
-        <v>241</v>
       </c>
       <c r="G392">
         <v>204</v>
@@ -13382,7 +13382,7 @@
         <v>0</v>
       </c>
       <c r="I392" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J392">
         <v>1</v>
@@ -13390,7 +13390,7 @@
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B393">
         <v>7</v>
@@ -13402,10 +13402,10 @@
         <v>20</v>
       </c>
       <c r="E393" t="s">
+        <v>239</v>
+      </c>
+      <c r="F393" t="s">
         <v>240</v>
-      </c>
-      <c r="F393" t="s">
-        <v>241</v>
       </c>
       <c r="G393">
         <v>200</v>
@@ -13414,7 +13414,7 @@
         <v>0</v>
       </c>
       <c r="I393" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J393">
         <v>1</v>
@@ -13422,7 +13422,7 @@
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B394">
         <v>15</v>
@@ -13434,10 +13434,10 @@
         <v>11</v>
       </c>
       <c r="E394" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F394" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G394">
         <v>250</v>
@@ -13446,7 +13446,7 @@
         <v>0</v>
       </c>
       <c r="I394" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J394">
         <v>1</v>
@@ -13454,7 +13454,7 @@
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B395">
         <v>15</v>
@@ -13466,10 +13466,10 @@
         <v>20</v>
       </c>
       <c r="E395" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F395" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G395">
         <v>250</v>
@@ -13478,7 +13478,7 @@
         <v>0</v>
       </c>
       <c r="I395" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J395">
         <v>1</v>
@@ -13486,7 +13486,7 @@
     </row>
     <row r="396" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B396">
         <v>11</v>
@@ -13498,10 +13498,10 @@
         <v>11</v>
       </c>
       <c r="E396" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F396" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G396">
         <v>250</v>
@@ -13510,7 +13510,7 @@
         <v>0</v>
       </c>
       <c r="I396" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J396">
         <v>1</v>
@@ -13518,7 +13518,7 @@
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B397">
         <v>11</v>
@@ -13530,10 +13530,10 @@
         <v>20</v>
       </c>
       <c r="E397" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F397" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G397">
         <v>210</v>
@@ -13542,7 +13542,7 @@
         <v>0</v>
       </c>
       <c r="I397" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J397">
         <v>1</v>
@@ -13550,22 +13550,22 @@
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B398">
+        <v>11</v>
+      </c>
+      <c r="C398" t="s">
+        <v>10</v>
+      </c>
+      <c r="D398" t="s">
+        <v>11</v>
+      </c>
+      <c r="E398" t="s">
         <v>245</v>
       </c>
-      <c r="B398">
-        <v>11</v>
-      </c>
-      <c r="C398" t="s">
-        <v>10</v>
-      </c>
-      <c r="D398" t="s">
-        <v>11</v>
-      </c>
-      <c r="E398" t="s">
-        <v>246</v>
-      </c>
       <c r="F398" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G398">
         <v>200</v>
@@ -13574,7 +13574,7 @@
         <v>0</v>
       </c>
       <c r="I398" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J398">
         <v>1</v>
@@ -13582,22 +13582,22 @@
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B399">
+        <v>11</v>
+      </c>
+      <c r="C399" t="s">
+        <v>10</v>
+      </c>
+      <c r="D399" t="s">
+        <v>20</v>
+      </c>
+      <c r="E399" t="s">
         <v>245</v>
       </c>
-      <c r="B399">
-        <v>11</v>
-      </c>
-      <c r="C399" t="s">
-        <v>10</v>
-      </c>
-      <c r="D399" t="s">
-        <v>20</v>
-      </c>
-      <c r="E399" t="s">
-        <v>246</v>
-      </c>
       <c r="F399" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G399">
         <v>200</v>
@@ -13606,7 +13606,7 @@
         <v>0</v>
       </c>
       <c r="I399" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J399">
         <v>1</v>
@@ -13614,7 +13614,7 @@
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B400">
         <v>11</v>
@@ -13626,10 +13626,10 @@
         <v>11</v>
       </c>
       <c r="E400" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F400" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G400">
         <v>225</v>
@@ -13638,7 +13638,7 @@
         <v>0</v>
       </c>
       <c r="I400" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J400">
         <v>1</v>
@@ -13646,7 +13646,7 @@
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B401">
         <v>11</v>
@@ -13658,10 +13658,10 @@
         <v>20</v>
       </c>
       <c r="E401" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F401" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G401">
         <v>200</v>
@@ -13670,7 +13670,7 @@
         <v>0</v>
       </c>
       <c r="I401" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J401">
         <v>1</v>
@@ -13678,7 +13678,7 @@
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B402">
         <v>4</v>
@@ -13690,10 +13690,10 @@
         <v>11</v>
       </c>
       <c r="E402" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F402" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G402">
         <v>200</v>
@@ -13702,7 +13702,7 @@
         <v>0</v>
       </c>
       <c r="I402" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J402">
         <v>1</v>
@@ -13710,7 +13710,7 @@
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B403">
         <v>4</v>
@@ -13722,10 +13722,10 @@
         <v>20</v>
       </c>
       <c r="E403" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F403" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G403">
         <v>200</v>
@@ -13734,7 +13734,7 @@
         <v>0</v>
       </c>
       <c r="I403" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J403">
         <v>1</v>
@@ -13742,7 +13742,7 @@
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B404">
         <v>2</v>
@@ -13754,10 +13754,10 @@
         <v>11</v>
       </c>
       <c r="E404" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F404" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G404">
         <v>100</v>
@@ -13774,7 +13774,7 @@
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B405">
         <v>2</v>
@@ -13786,10 +13786,10 @@
         <v>20</v>
       </c>
       <c r="E405" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F405" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G405">
         <v>100</v>
@@ -13806,7 +13806,7 @@
     </row>
     <row r="406" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B406">
         <v>2</v>
@@ -13818,10 +13818,10 @@
         <v>11</v>
       </c>
       <c r="E406" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F406" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G406">
         <v>100</v>
@@ -13838,7 +13838,7 @@
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B407">
         <v>2</v>
@@ -13850,10 +13850,10 @@
         <v>20</v>
       </c>
       <c r="E407" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F407" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G407">
         <v>100</v>
@@ -13870,7 +13870,7 @@
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B408">
         <v>2</v>
@@ -13882,10 +13882,10 @@
         <v>11</v>
       </c>
       <c r="E408" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F408" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G408">
         <v>100</v>
@@ -13902,7 +13902,7 @@
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B409">
         <v>2</v>
@@ -13914,10 +13914,10 @@
         <v>20</v>
       </c>
       <c r="E409" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F409" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G409">
         <v>100</v>
@@ -13934,7 +13934,7 @@
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B410">
         <v>26</v>
@@ -13946,10 +13946,10 @@
         <v>11</v>
       </c>
       <c r="E410" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F410" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G410">
         <v>800</v>
@@ -13958,7 +13958,7 @@
         <v>0</v>
       </c>
       <c r="I410" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J410">
         <v>1</v>
@@ -13966,7 +13966,7 @@
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B411">
         <v>26</v>
@@ -13978,10 +13978,10 @@
         <v>20</v>
       </c>
       <c r="E411" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F411" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G411">
         <v>800</v>
@@ -13990,7 +13990,7 @@
         <v>0</v>
       </c>
       <c r="I411" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J411">
         <v>1</v>
@@ -13998,7 +13998,7 @@
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B412">
         <v>26</v>
@@ -14010,10 +14010,10 @@
         <v>11</v>
       </c>
       <c r="E412" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F412" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G412">
         <v>200</v>
@@ -14022,7 +14022,7 @@
         <v>0</v>
       </c>
       <c r="I412" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J412">
         <v>1</v>
@@ -14030,7 +14030,7 @@
     </row>
     <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B413">
         <v>26</v>
@@ -14042,10 +14042,10 @@
         <v>20</v>
       </c>
       <c r="E413" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F413" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G413">
         <v>150</v>
@@ -14054,7 +14054,7 @@
         <v>0</v>
       </c>
       <c r="I413" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J413">
         <v>1</v>
@@ -14062,7 +14062,7 @@
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B414">
         <v>26</v>
@@ -14074,10 +14074,10 @@
         <v>11</v>
       </c>
       <c r="E414" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F414" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G414">
         <v>150</v>
@@ -14086,7 +14086,7 @@
         <v>0</v>
       </c>
       <c r="I414" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J414">
         <v>1</v>
@@ -14094,7 +14094,7 @@
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B415">
         <v>26</v>
@@ -14106,10 +14106,10 @@
         <v>20</v>
       </c>
       <c r="E415" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F415" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G415">
         <v>150</v>
@@ -14118,7 +14118,7 @@
         <v>0</v>
       </c>
       <c r="I415" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J415">
         <v>1</v>
@@ -14126,7 +14126,7 @@
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B416">
         <v>8</v>
@@ -14138,10 +14138,10 @@
         <v>11</v>
       </c>
       <c r="E416" t="s">
+        <v>254</v>
+      </c>
+      <c r="F416" t="s">
         <v>255</v>
-      </c>
-      <c r="F416" t="s">
-        <v>256</v>
       </c>
       <c r="G416">
         <v>700</v>
@@ -14150,7 +14150,7 @@
         <v>0</v>
       </c>
       <c r="I416" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J416">
         <v>1</v>
@@ -14158,7 +14158,7 @@
     </row>
     <row r="417" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B417">
         <v>8</v>
@@ -14170,10 +14170,10 @@
         <v>20</v>
       </c>
       <c r="E417" t="s">
+        <v>254</v>
+      </c>
+      <c r="F417" t="s">
         <v>255</v>
-      </c>
-      <c r="F417" t="s">
-        <v>256</v>
       </c>
       <c r="G417">
         <v>800</v>
@@ -14182,7 +14182,7 @@
         <v>0</v>
       </c>
       <c r="I417" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J417">
         <v>1</v>
@@ -14190,7 +14190,7 @@
     </row>
     <row r="418" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B418">
         <v>8</v>
@@ -14202,10 +14202,10 @@
         <v>11</v>
       </c>
       <c r="E418" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F418" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G418">
         <v>500</v>
@@ -14214,7 +14214,7 @@
         <v>0</v>
       </c>
       <c r="I418" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J418">
         <v>1</v>
@@ -14222,7 +14222,7 @@
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B419">
         <v>8</v>
@@ -14234,10 +14234,10 @@
         <v>20</v>
       </c>
       <c r="E419" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F419" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G419">
         <v>500</v>
@@ -14246,7 +14246,7 @@
         <v>0</v>
       </c>
       <c r="I419" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J419">
         <v>1</v>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B420">
         <v>8</v>
@@ -14266,10 +14266,10 @@
         <v>11</v>
       </c>
       <c r="E420" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F420" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G420">
         <v>200</v>
@@ -14278,7 +14278,7 @@
         <v>0</v>
       </c>
       <c r="I420" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J420">
         <v>1</v>
@@ -14286,7 +14286,7 @@
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B421">
         <v>8</v>
@@ -14298,10 +14298,10 @@
         <v>20</v>
       </c>
       <c r="E421" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F421" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G421">
         <v>200</v>
@@ -14310,7 +14310,7 @@
         <v>0</v>
       </c>
       <c r="I421" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J421">
         <v>1</v>
@@ -14318,7 +14318,7 @@
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B422">
         <v>8</v>
@@ -14330,10 +14330,10 @@
         <v>11</v>
       </c>
       <c r="E422" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F422" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G422">
         <v>250</v>
@@ -14342,7 +14342,7 @@
         <v>0</v>
       </c>
       <c r="I422" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J422">
         <v>1</v>
@@ -14350,7 +14350,7 @@
     </row>
     <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B423">
         <v>8</v>
@@ -14362,10 +14362,10 @@
         <v>20</v>
       </c>
       <c r="E423" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F423" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G423">
         <v>250</v>
@@ -14374,7 +14374,7 @@
         <v>0</v>
       </c>
       <c r="I423" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J423">
         <v>1</v>
@@ -14382,7 +14382,7 @@
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B424">
         <v>8</v>
@@ -14394,10 +14394,10 @@
         <v>11</v>
       </c>
       <c r="E424" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F424" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G424">
         <v>800</v>
@@ -14406,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="I424" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J424">
         <v>1</v>
@@ -14414,7 +14414,7 @@
     </row>
     <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B425">
         <v>8</v>
@@ -14426,10 +14426,10 @@
         <v>20</v>
       </c>
       <c r="E425" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F425" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G425">
         <v>800</v>
@@ -14438,7 +14438,7 @@
         <v>0</v>
       </c>
       <c r="I425" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J425">
         <v>1</v>
@@ -14446,7 +14446,7 @@
     </row>
     <row r="426" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B426">
         <v>9</v>
@@ -14458,10 +14458,10 @@
         <v>11</v>
       </c>
       <c r="E426" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F426" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G426">
         <v>200</v>
@@ -14470,7 +14470,7 @@
         <v>0</v>
       </c>
       <c r="I426" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J426">
         <v>1</v>
@@ -14478,7 +14478,7 @@
     </row>
     <row r="427" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B427">
         <v>9</v>
@@ -14490,10 +14490,10 @@
         <v>20</v>
       </c>
       <c r="E427" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F427" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G427">
         <v>200</v>
@@ -14502,7 +14502,7 @@
         <v>0</v>
       </c>
       <c r="I427" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J427">
         <v>1</v>
@@ -14510,7 +14510,7 @@
     </row>
     <row r="428" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B428">
         <v>6</v>
@@ -14522,10 +14522,10 @@
         <v>11</v>
       </c>
       <c r="E428" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F428" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G428">
         <v>200</v>
@@ -14534,7 +14534,7 @@
         <v>0</v>
       </c>
       <c r="I428" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J428">
         <v>1</v>
@@ -14542,7 +14542,7 @@
     </row>
     <row r="429" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B429">
         <v>6</v>
@@ -14554,10 +14554,10 @@
         <v>11</v>
       </c>
       <c r="E429" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F429" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G429">
         <v>200</v>
@@ -14566,7 +14566,7 @@
         <v>0</v>
       </c>
       <c r="I429" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J429">
         <v>1</v>
@@ -14574,7 +14574,7 @@
     </row>
     <row r="430" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B430">
         <v>6</v>
@@ -14586,10 +14586,10 @@
         <v>11</v>
       </c>
       <c r="E430" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F430" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G430">
         <v>200</v>
@@ -14598,7 +14598,7 @@
         <v>0</v>
       </c>
       <c r="I430" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J430">
         <v>1</v>
@@ -14606,7 +14606,7 @@
     </row>
     <row r="431" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B431">
         <v>6</v>
@@ -14618,10 +14618,10 @@
         <v>20</v>
       </c>
       <c r="E431" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F431" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G431">
         <v>200</v>
@@ -14630,7 +14630,7 @@
         <v>0</v>
       </c>
       <c r="I431" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J431">
         <v>1</v>
@@ -14638,7 +14638,7 @@
     </row>
     <row r="432" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B432">
         <v>6</v>
@@ -14650,10 +14650,10 @@
         <v>20</v>
       </c>
       <c r="E432" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F432" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G432">
         <v>200</v>
@@ -14662,7 +14662,7 @@
         <v>0</v>
       </c>
       <c r="I432" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J432">
         <v>1</v>
@@ -14670,7 +14670,7 @@
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B433">
         <v>6</v>
@@ -14682,10 +14682,10 @@
         <v>20</v>
       </c>
       <c r="E433" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F433" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G433">
         <v>200</v>
@@ -14694,7 +14694,7 @@
         <v>0</v>
       </c>
       <c r="I433" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J433">
         <v>1</v>
@@ -14702,7 +14702,7 @@
     </row>
     <row r="434" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B434">
         <v>4</v>
@@ -14714,10 +14714,10 @@
         <v>11</v>
       </c>
       <c r="E434" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F434" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G434">
         <v>200</v>
@@ -14734,7 +14734,7 @@
     </row>
     <row r="435" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B435">
         <v>4</v>
@@ -14746,10 +14746,10 @@
         <v>11</v>
       </c>
       <c r="E435" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F435" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G435">
         <v>200</v>
@@ -14766,7 +14766,7 @@
     </row>
     <row r="436" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B436">
         <v>4</v>
@@ -14778,10 +14778,10 @@
         <v>11</v>
       </c>
       <c r="E436" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F436" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G436">
         <v>200</v>
@@ -14798,7 +14798,7 @@
     </row>
     <row r="437" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B437">
         <v>4</v>
@@ -14810,10 +14810,10 @@
         <v>20</v>
       </c>
       <c r="E437" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F437" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G437">
         <v>200</v>
@@ -14830,7 +14830,7 @@
     </row>
     <row r="438" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B438">
         <v>4</v>
@@ -14842,10 +14842,10 @@
         <v>20</v>
       </c>
       <c r="E438" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F438" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G438">
         <v>200</v>
@@ -14862,7 +14862,7 @@
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B439">
         <v>4</v>
@@ -14874,10 +14874,10 @@
         <v>20</v>
       </c>
       <c r="E439" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F439" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G439">
         <v>200</v>
@@ -14894,7 +14894,7 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B440">
         <v>3</v>
@@ -14906,10 +14906,10 @@
         <v>20</v>
       </c>
       <c r="E440" t="s">
+        <v>268</v>
+      </c>
+      <c r="F440" t="s">
         <v>269</v>
-      </c>
-      <c r="F440" t="s">
-        <v>270</v>
       </c>
       <c r="G440">
         <v>800</v>
@@ -14926,7 +14926,7 @@
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B441">
         <v>3</v>
@@ -14938,10 +14938,10 @@
         <v>11</v>
       </c>
       <c r="E441" t="s">
+        <v>268</v>
+      </c>
+      <c r="F441" t="s">
         <v>269</v>
-      </c>
-      <c r="F441" t="s">
-        <v>270</v>
       </c>
       <c r="G441">
         <v>800</v>
@@ -14958,7 +14958,7 @@
     </row>
     <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B442">
         <v>3</v>
@@ -14970,10 +14970,10 @@
         <v>20</v>
       </c>
       <c r="E442" t="s">
+        <v>268</v>
+      </c>
+      <c r="F442" t="s">
         <v>269</v>
-      </c>
-      <c r="F442" t="s">
-        <v>270</v>
       </c>
       <c r="G442">
         <v>800</v>
@@ -14990,7 +14990,7 @@
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B443">
         <v>3</v>
@@ -15002,10 +15002,10 @@
         <v>11</v>
       </c>
       <c r="E443" t="s">
+        <v>268</v>
+      </c>
+      <c r="F443" t="s">
         <v>269</v>
-      </c>
-      <c r="F443" t="s">
-        <v>270</v>
       </c>
       <c r="G443">
         <v>800</v>
@@ -15022,7 +15022,7 @@
     </row>
     <row r="444" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B444">
         <v>3</v>
@@ -15034,10 +15034,10 @@
         <v>20</v>
       </c>
       <c r="E444" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F444" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G444">
         <v>800</v>
@@ -15054,7 +15054,7 @@
     </row>
     <row r="445" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B445">
         <v>3</v>
@@ -15066,10 +15066,10 @@
         <v>11</v>
       </c>
       <c r="E445" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F445" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G445">
         <v>800</v>
@@ -15086,7 +15086,7 @@
     </row>
     <row r="446" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B446">
         <v>16</v>
@@ -15098,10 +15098,10 @@
         <v>11</v>
       </c>
       <c r="E446" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F446" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G446">
         <v>800</v>
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="I446" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J446">
         <v>1</v>
@@ -15118,7 +15118,7 @@
     </row>
     <row r="447" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B447">
         <v>16</v>
@@ -15130,10 +15130,10 @@
         <v>20</v>
       </c>
       <c r="E447" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F447" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G447">
         <v>800</v>
@@ -15142,7 +15142,7 @@
         <v>0</v>
       </c>
       <c r="I447" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J447">
         <v>1</v>
@@ -15150,7 +15150,7 @@
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B448">
         <v>16</v>
@@ -15162,10 +15162,10 @@
         <v>11</v>
       </c>
       <c r="E448" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F448" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G448">
         <v>400</v>
@@ -15174,7 +15174,7 @@
         <v>0</v>
       </c>
       <c r="I448" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J448">
         <v>1</v>
@@ -15182,7 +15182,7 @@
     </row>
     <row r="449" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B449">
         <v>16</v>
@@ -15194,10 +15194,10 @@
         <v>11</v>
       </c>
       <c r="E449" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F449" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G449">
         <v>400</v>
@@ -15206,7 +15206,7 @@
         <v>0</v>
       </c>
       <c r="I449" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J449">
         <v>1</v>
@@ -15214,7 +15214,7 @@
     </row>
     <row r="450" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B450">
         <v>16</v>
@@ -15226,10 +15226,10 @@
         <v>20</v>
       </c>
       <c r="E450" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F450" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G450">
         <v>400</v>
@@ -15238,7 +15238,7 @@
         <v>0</v>
       </c>
       <c r="I450" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J450">
         <v>1</v>
@@ -15246,7 +15246,7 @@
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B451">
         <v>16</v>
@@ -15258,10 +15258,10 @@
         <v>20</v>
       </c>
       <c r="E451" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F451" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G451">
         <v>400</v>
@@ -15270,7 +15270,7 @@
         <v>0</v>
       </c>
       <c r="I451" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J451">
         <v>1</v>
@@ -15278,7 +15278,7 @@
     </row>
     <row r="452" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B452">
         <v>3</v>
@@ -15290,10 +15290,10 @@
         <v>11</v>
       </c>
       <c r="E452" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F452" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G452">
         <v>200</v>
@@ -15302,7 +15302,7 @@
         <v>0</v>
       </c>
       <c r="I452" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J452">
         <v>1</v>
@@ -15310,7 +15310,7 @@
     </row>
     <row r="453" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B453">
         <v>3</v>
@@ -15322,10 +15322,10 @@
         <v>20</v>
       </c>
       <c r="E453" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F453" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G453">
         <v>200</v>
@@ -15334,7 +15334,7 @@
         <v>0</v>
       </c>
       <c r="I453" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J453">
         <v>1</v>
@@ -15354,10 +15354,10 @@
         <v>11</v>
       </c>
       <c r="E454" t="s">
+        <v>298</v>
+      </c>
+      <c r="F454" t="s">
         <v>299</v>
-      </c>
-      <c r="F454" t="s">
-        <v>300</v>
       </c>
       <c r="G454">
         <v>300</v>
@@ -15366,7 +15366,7 @@
         <v>0</v>
       </c>
       <c r="I454" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J454">
         <v>2</v>
@@ -15386,10 +15386,10 @@
         <v>20</v>
       </c>
       <c r="E455" t="s">
+        <v>298</v>
+      </c>
+      <c r="F455" t="s">
         <v>299</v>
-      </c>
-      <c r="F455" t="s">
-        <v>300</v>
       </c>
       <c r="G455">
         <v>300</v>
@@ -15398,7 +15398,7 @@
         <v>0</v>
       </c>
       <c r="I455" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J455">
         <v>2</v>
@@ -15418,10 +15418,10 @@
         <v>11</v>
       </c>
       <c r="E456" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F456" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G456">
         <v>800</v>
@@ -15430,7 +15430,7 @@
         <v>0</v>
       </c>
       <c r="I456" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J456">
         <v>2</v>
@@ -15450,10 +15450,10 @@
         <v>20</v>
       </c>
       <c r="E457" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F457" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G457">
         <v>800</v>
@@ -15462,7 +15462,7 @@
         <v>0</v>
       </c>
       <c r="I457" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J457">
         <v>2</v>
@@ -15482,10 +15482,10 @@
         <v>11</v>
       </c>
       <c r="E458" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F458" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G458">
         <v>300</v>
@@ -15494,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="I458" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J458">
         <v>2</v>
@@ -15514,10 +15514,10 @@
         <v>20</v>
       </c>
       <c r="E459" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F459" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G459">
         <v>250</v>
@@ -15526,7 +15526,7 @@
         <v>0</v>
       </c>
       <c r="I459" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J459">
         <v>2</v>
@@ -15546,10 +15546,10 @@
         <v>11</v>
       </c>
       <c r="E460" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F460" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G460">
         <v>250</v>
@@ -15558,7 +15558,7 @@
         <v>0</v>
       </c>
       <c r="I460" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J460">
         <v>2</v>
@@ -15578,10 +15578,10 @@
         <v>20</v>
       </c>
       <c r="E461" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F461" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G461">
         <v>250</v>
@@ -15590,14 +15590,13 @@
         <v>0</v>
       </c>
       <c r="I461" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J461">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H461" xr:uid="{29FBF8AE-8F61-493B-A3DA-32DCBB1B5FAA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H233">
     <sortCondition descending="1" ref="A2:A233"/>
   </sortState>
@@ -15620,13 +15619,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B1" t="s">
         <v>271</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>272</v>
-      </c>
-      <c r="C1" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -15634,10 +15633,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C2" t="s">
         <v>274</v>
-      </c>
-      <c r="C2" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -15645,10 +15644,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3" t="s">
         <v>276</v>
-      </c>
-      <c r="C3" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -15656,10 +15655,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C4" t="s">
         <v>278</v>
-      </c>
-      <c r="C4" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -15667,10 +15666,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>279</v>
+      </c>
+      <c r="C5" t="s">
         <v>280</v>
-      </c>
-      <c r="C5" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -15678,10 +15677,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>281</v>
+      </c>
+      <c r="C6" t="s">
         <v>282</v>
-      </c>
-      <c r="C6" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -15689,10 +15688,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -15700,10 +15699,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>284</v>
+      </c>
+      <c r="C8" t="s">
         <v>285</v>
-      </c>
-      <c r="C8" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -15711,10 +15710,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>286</v>
+      </c>
+      <c r="C9" t="s">
         <v>287</v>
-      </c>
-      <c r="C9" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
@@ -15722,7 +15721,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -15774,6 +15773,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001AF5FC5DD832BE4DBA6B24560DD3ADC0" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d40b3e6283001fb57e5088f84fb23d5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4" xmlns:ns3="http://schemas.microsoft.com/sharepoint.v3" xmlns:ns4="http://schemas.microsoft.com/sharepoint/v3/fields" xmlns:ns5="8b03727f-4454-4722-b3e6-018d8dcaf2fd" xmlns:ns6="ed970698-2d60-4bab-a048-d9be527522d9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="aadbb8160917885bdc8cfb32badaafe9" ns1:_="" ns2:_="" ns3:_="" ns4:_="" ns5:_="" ns6:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -16244,35 +16257,44 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="29f62856-1543-49d4-a736-4569d363f533" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3B0691D-AF24-45AB-9162-F2630B172446}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="ed970698-2d60-4bab-a048-d9be527522d9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="8b03727f-4454-4722-b3e6-018d8dcaf2fd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
-    <ds:schemaRef ds:uri="ed970698-2d60-4bab-a048-d9be527522d9"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E6B34BE-5823-4045-916A-22F5417AF5E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA014E12-2A38-4F6C-AEC2-E258ABAB897D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC2A5959-209C-4A1D-8C12-ADB78C841E40}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16293,20 +16315,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA014E12-2A38-4F6C-AEC2-E258ABAB897D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E6B34BE-5823-4045-916A-22F5417AF5E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>